--- a/verification/cases/roundtrip/formulas_logical/init.xlsx
+++ b/verification/cases/roundtrip/formulas_logical/init.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/cells/tests/excel-roundtrips/data/logical/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF346DB-2E12-E746-B802-9A91BFE91B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{796EBC5E-7027-4AD5-BF1B-8336F68B9839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="660" windowWidth="28220" windowHeight="17960" xr2:uid="{7962C6A1-ACEE-2046-8E2E-AB24DAF72AAB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7962C6A1-ACEE-2046-8E2E-AB24DAF72AAB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1351,7 +1351,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1374,19 +1374,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04935397-B27E-9144-8F2D-75EF70F7049B}">
   <dimension ref="B2:M226"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="54.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.69921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
@@ -1400,7 +1400,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1412,7 +1412,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1426,7 +1426,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="b">
         <v>1</v>
       </c>
@@ -1442,7 +1442,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="b">
         <v>0</v>
       </c>
@@ -1458,7 +1458,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
@@ -1474,7 +1474,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
@@ -1490,7 +1490,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
@@ -1506,7 +1506,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1522,7 +1522,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1538,7 +1538,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1552,7 +1552,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>13</v>
       </c>
@@ -1586,7 +1586,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1603,7 +1603,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -1617,7 +1617,7 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -1631,7 +1631,7 @@
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>15</v>
       </c>
@@ -1645,7 +1645,7 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
         <v>3</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="b">
         <v>1</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="b">
         <v>0</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4">
         <v>1</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4">
         <v>0</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4">
         <v>-1</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
         <v>42.5</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>16</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>17</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="e">
         <v>#VALUE!</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>18</v>
       </c>
@@ -2236,7 +2236,7 @@
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="8" t="s">
         <v>3</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="b">
         <v>1</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="b">
         <v>0</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="4">
         <v>1</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B40" s="4">
         <v>0</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
         <v>-1</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B42" s="4">
         <v>42.5</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>16</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>17</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="e">
         <v>#VALUE!</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
         <v>19</v>
       </c>
@@ -2827,7 +2827,7 @@
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B52" s="8" t="s">
         <v>3</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="b">
         <v>1</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="b">
         <v>0</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B55" s="4">
         <v>1</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
         <v>0</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B57" s="4">
         <v>-1</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B58" s="4">
         <v>42.5</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
         <v>16</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>17</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="e">
         <v>#VALUE!</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -3418,7 +3418,7 @@
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
         <v>20</v>
       </c>
@@ -3432,7 +3432,7 @@
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68" s="9" t="s">
         <v>21</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="b">
         <v>1</v>
       </c>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B70" s="4" t="b">
         <v>0</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B71" s="4">
         <v>1</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B72" s="4">
         <v>0</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B73" s="4">
         <v>-1</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
         <v>42.5</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B75" s="4" t="s">
         <v>16</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
         <v>17</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="e">
         <v>#VALUE!</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -3553,7 +3553,7 @@
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
@@ -3567,7 +3567,7 @@
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
         <v>22</v>
       </c>
@@ -3583,7 +3583,7 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B84" s="9" t="s">
         <v>23</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B85" s="10">
         <v>1</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B86" s="10">
         <v>2</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B87" s="10">
         <v>3</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B88" s="10">
         <v>4</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B89" s="10">
         <v>5</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B90" s="10">
         <v>6</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B91" s="10">
         <v>7</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B92" s="10">
         <v>8</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B93" s="10">
         <v>9</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B94" s="10">
         <v>10</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B95" s="10">
         <v>11</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B96" s="10">
         <v>12</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B97" s="10">
         <v>13</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B98" s="10">
         <v>14</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B99" s="10">
         <v>15</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B100" s="10">
         <v>16</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B101" s="10">
         <v>17</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B102" s="10">
         <v>18</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B103" s="10">
         <v>19</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B104" s="10">
         <v>20</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B105" s="10">
         <v>21</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B106" s="10">
         <v>22</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B109" s="3" t="s">
         <v>87</v>
       </c>
@@ -4239,7 +4239,7 @@
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
     </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B111" s="9" t="s">
         <v>23</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B112" s="10">
         <v>1</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B113" s="10">
         <v>2</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B114" s="10">
         <v>3</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B115" s="10">
         <v>4</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B116" s="10">
         <v>5</v>
       </c>
@@ -4392,7 +4392,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B117" s="10">
         <v>6</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="118" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B118" s="10">
         <v>7</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B119" s="10">
         <v>8</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B120" s="10">
         <v>9</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B121" s="10">
         <v>10</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B122" s="10">
         <v>11</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B123" s="10">
         <v>12</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="124" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B124" s="10">
         <v>13</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="125" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B125" s="10">
         <v>14</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="128" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B128" s="3" t="s">
         <v>121</v>
       </c>
@@ -4642,7 +4642,7 @@
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
     </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B130" s="9" t="s">
         <v>23</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B131" s="10">
         <v>1</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B132" s="10">
         <v>2</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B133" s="10">
         <v>3</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B134" s="10">
         <v>4</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B135" s="10">
         <v>5</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B136" s="10">
         <v>6</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B137" s="10">
         <v>7</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B138" s="10">
         <v>8</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B139" s="10">
         <v>9</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B140" s="10">
         <v>10</v>
       </c>
@@ -4925,7 +4925,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <v>11</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B142" s="10">
         <v>12</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B143" s="10">
         <v>13</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B144" s="10">
         <v>14</v>
       </c>
@@ -5029,7 +5029,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="145" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B145" s="10">
         <v>15</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="146" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B146" s="10">
         <v>16</v>
       </c>
@@ -5081,7 +5081,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="149" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B149" s="3" t="s">
         <v>158</v>
       </c>
@@ -5097,7 +5097,7 @@
       <c r="L149" s="3"/>
       <c r="M149" s="3"/>
     </row>
-    <row r="151" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B151" s="9" t="s">
         <v>23</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="152" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B152" s="10">
         <v>1</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="153" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B153" s="10">
         <v>2</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="154" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B154" s="10">
         <v>3</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="155" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B155" s="10">
         <v>4</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="156" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B156" s="10">
         <v>5</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="157" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B157" s="10">
         <v>6</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="158" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B158" s="10">
         <v>7</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="159" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B159" s="10">
         <v>8</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="160" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B160" s="10">
         <v>9</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="161" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B161" s="10">
         <v>10</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="162" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B162" s="10">
         <v>11</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="163" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B163" s="10">
         <v>12</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="164" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B164" s="10">
         <v>13</v>
       </c>
@@ -5456,7 +5456,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="165" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B165" s="10">
         <v>14</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="166" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B166" s="10">
         <v>15</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="167" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <v>16</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="170" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B170" s="3" t="s">
         <v>195</v>
       </c>
@@ -5550,7 +5550,7 @@
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
     </row>
-    <row r="172" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B172" s="9" t="s">
         <v>23</v>
       </c>
@@ -5573,7 +5573,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="173" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B173" s="10">
         <v>1</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="174" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B174" s="10">
         <v>2</v>
       </c>
@@ -5625,7 +5625,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="175" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B175" s="10">
         <v>3</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="176" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B176" s="10">
         <v>4</v>
       </c>
@@ -5677,7 +5677,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="177" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B177" s="10">
         <v>5</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="178" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B178" s="10">
         <v>6</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="179" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B179" s="10">
         <v>7</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="180" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B180" s="10">
         <v>8</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="181" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B181" s="10">
         <v>9</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="182" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B182" s="10">
         <v>10</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="183" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B183" s="10">
         <v>11</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B184" s="10">
         <v>12</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="185" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B185" s="10">
         <v>13</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="186" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B186" s="10">
         <v>14</v>
       </c>
@@ -5937,7 +5937,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="189" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B189" s="3" t="s">
         <v>220</v>
       </c>
@@ -5953,7 +5953,7 @@
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
     </row>
-    <row r="191" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B191" s="9" t="s">
         <v>23</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="192" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B192" s="10">
         <v>1</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="193" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B193" s="10">
         <v>2</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="194" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B194" s="10">
         <v>3</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="195" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B195" s="10">
         <v>4</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="196" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B196" s="10">
         <v>5</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="197" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B197" s="10">
         <v>6</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="198" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B198" s="10">
         <v>7</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="199" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B199" s="10">
         <v>8</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="200" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B200" s="10">
         <v>9</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="201" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B201" s="10">
         <v>10</v>
       </c>
@@ -6236,7 +6236,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="202" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B202" s="10">
         <v>11</v>
       </c>
@@ -6262,7 +6262,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="203" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B203" s="10">
         <v>12</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="204" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B204" s="10">
         <v>13</v>
       </c>
@@ -6314,7 +6314,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="205" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B205" s="10">
         <v>14</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="206" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B206" s="10">
         <v>15</v>
       </c>
@@ -6366,7 +6366,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="209" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B209" s="3" t="s">
         <v>254</v>
       </c>
@@ -6382,7 +6382,7 @@
       <c r="L209" s="3"/>
       <c r="M209" s="3"/>
     </row>
-    <row r="211" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B211" s="9" t="s">
         <v>23</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="212" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B212" s="10">
         <v>1</v>
       </c>
@@ -6431,7 +6431,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="213" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B213" s="10">
         <v>2</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="214" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B214" s="10">
         <v>3</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="215" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B215" s="10">
         <v>4</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="216" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B216" s="10">
         <v>5</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="217" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B217" s="10">
         <v>6</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="218" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B218" s="10">
         <v>7</v>
       </c>
@@ -6587,7 +6587,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="219" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B219" s="10">
         <v>8</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="220" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B220" s="10">
         <v>9</v>
       </c>
@@ -6639,7 +6639,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="221" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B221" s="10">
         <v>10</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="222" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B222" s="10">
         <v>11</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="223" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B223" s="10">
         <v>12</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="224" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B224" s="10">
         <v>13</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="225" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B225" s="10">
         <v>14</v>
       </c>
@@ -6769,7 +6769,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="226" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B226" s="10">
         <v>15</v>
       </c>
